--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -40144,12 +40144,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40174,7 +40174,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -40183,81 +40183,100 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="O225" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="R225" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.4018298584161838</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40284,17 +40303,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40319,7 +40338,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -40328,26 +40347,103 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O226" t="n">
-        <v>2</v>
-      </c>
-      <c r="P226" t="n">
-        <v>2</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>43</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
@@ -40356,7 +40452,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -40364,9 +40460,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -40374,47 +40475,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40441,17 +40542,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40485,173 +40586,81 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227" t="n">
-        <v>2</v>
-      </c>
-      <c r="P227" t="n">
-        <v>2</v>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
         <v>1</v>
       </c>
+      <c r="R227" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40683,12 +40692,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40713,7 +40722,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -40727,76 +40736,88 @@
       <c r="O228" t="n">
         <v>2</v>
       </c>
+      <c r="P228" t="n">
+        <v>2</v>
+      </c>
       <c r="R228" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40823,7 +40844,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -40858,7 +40879,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -40867,26 +40888,106 @@
         </is>
       </c>
       <c r="N229" t="n">
+        <v>2</v>
+      </c>
+      <c r="O229" t="n">
+        <v>2</v>
+      </c>
+      <c r="P229" t="n">
+        <v>2</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
         <v>1</v>
-      </c>
-      <c r="O229" t="n">
-        <v>1</v>
-      </c>
-      <c r="P229" t="n">
-        <v>1</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -40980,17 +41081,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41024,173 +41125,81 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
-      </c>
-      <c r="P230" t="n">
-        <v>1</v>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41222,12 +41231,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41252,7 +41261,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41261,81 +41270,93 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P231" t="n">
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41362,7 +41383,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -41397,7 +41418,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -41406,26 +41427,106 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P232" t="n">
-        <v>2</v>
-      </c>
-      <c r="R232" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
@@ -41519,17 +41620,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41563,173 +41664,81 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>2</v>
-      </c>
-      <c r="P233" t="n">
-        <v>2</v>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41761,12 +41770,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41791,7 +41800,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -41800,81 +41809,93 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O234" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="P234" t="n">
+        <v>2</v>
       </c>
       <c r="R234" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41901,7 +41922,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -41936,7 +41957,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -41953,18 +41974,98 @@
       <c r="P235" t="n">
         <v>2</v>
       </c>
-      <c r="R235" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -42058,17 +42159,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42102,173 +42203,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>2</v>
-      </c>
-      <c r="P236" t="n">
-        <v>2</v>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
         <v>1</v>
       </c>
+      <c r="R236" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42300,12 +42309,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42330,90 +42339,102 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O237" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P237" t="n">
+        <v>2</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42440,17 +42461,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42475,37 +42496,115 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P238" t="n">
+        <v>2</v>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -42514,22 +42613,17 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
         </is>
       </c>
       <c r="AT238" t="n">
@@ -42537,47 +42631,47 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42604,17 +42698,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42653,170 +42747,76 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
+      <c r="AT239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP239" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT239" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU239" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV239" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -42848,12 +42848,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42900,68 +42900,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42988,17 +43007,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43037,17 +43056,34 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -43055,6 +43091,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43067,7 +43161,7 @@
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
@@ -43077,7 +43171,7 @@
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT241" t="n">
@@ -43085,47 +43179,47 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43152,17 +43246,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43201,168 +43295,477 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V242" t="inlineStr">
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="W242" t="inlineStr">
+      <c r="AT243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X242" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>Meslinger</t>
         </is>
       </c>
-      <c r="Y242" t="inlineStr">
+      <c r="Y244" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr">
+      <c r="Z244" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA242" t="inlineStr">
+      <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB242" t="inlineStr">
+      <c r="AB244" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC242" t="inlineStr">
+      <c r="AC244" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD242" t="inlineStr">
+      <c r="AD244" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE242" t="inlineStr">
+      <c r="AE244" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF242" t="inlineStr">
+      <c r="AF244" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG242" t="inlineStr">
+      <c r="AG244" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH242" t="inlineStr">
+      <c r="AH244" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI242" t="inlineStr">
+      <c r="AI244" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ242" t="inlineStr">
+      <c r="AJ244" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK242" t="inlineStr">
+      <c r="AK244" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM242" t="inlineStr">
+      <c r="AM244" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN242" t="b">
+      <c r="AN244" t="b">
         <v>1</v>
       </c>
-      <c r="AO242" t="inlineStr">
+      <c r="AO244" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP242" t="inlineStr">
+      <c r="AP244" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ242" t="inlineStr">
+      <c r="AQ244" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR242" t="inlineStr">
+      <c r="AR244" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS242" t="inlineStr">
+      <c r="AS244" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="AT242" t="n">
+      <c r="AT244" t="n">
         <v>2</v>
       </c>
-      <c r="AU242" t="inlineStr">
+      <c r="AU244" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV242" t="inlineStr">
+      <c r="AV244" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW242" t="inlineStr">
+      <c r="AW244" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX242" t="inlineStr">
+      <c r="AX244" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY242" t="inlineStr">
+      <c r="AY244" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ242" t="inlineStr">
+      <c r="AZ244" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA242" t="inlineStr">
+      <c r="BA244" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB242" t="inlineStr">
+      <c r="BB244" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC242" t="inlineStr">
+      <c r="BC244" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -43484,7 +43887,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -43494,7 +43897,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -43514,7 +43917,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -43546,7 +43949,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1406</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -39232,13 +39232,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -39396,10 +39396,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -42703,12 +42703,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42733,22 +42733,22 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -42781,42 +42781,42 @@
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42848,12 +42848,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42900,87 +42900,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43007,7 +42988,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -43056,98 +43037,23 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -43246,17 +43152,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43295,76 +43201,170 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43396,12 +43396,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -43448,87 +43448,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43555,7 +43536,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -43604,98 +43585,23 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -43766,6 +43672,245 @@
         </is>
       </c>
       <c r="BC244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -43887,7 +44032,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -43897,7 +44042,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -43949,7 +44094,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -40183,13 +40183,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O225" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R225" t="n">
-        <v>0.4018298584161838</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -40347,10 +40347,10 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O226" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
@@ -43580,13 +43580,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -43744,10 +43744,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -39193,12 +39193,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39232,100 +39232,84 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O220" t="n">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.004246542694163248</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -39352,7 +39336,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -39401,98 +39385,23 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
+      <c r="R221" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -39591,17 +39500,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39635,81 +39544,175 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39741,12 +39744,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39793,87 +39796,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39900,7 +39884,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -39949,98 +39933,23 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -40139,17 +40048,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40183,22 +40092,39 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
-        <v>42</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.3924849779879006</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -40206,6 +40132,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40228,7 +40212,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -40241,42 +40225,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40303,7 +40287,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -40352,98 +40336,23 @@
       <c r="O226" t="n">
         <v>42</v>
       </c>
+      <c r="R226" t="n">
+        <v>0.3924849779879006</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U226" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>Mässling</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG226" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ226" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK226" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN226" t="b">
-        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
@@ -40542,17 +40451,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40577,7 +40486,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -40586,81 +40495,175 @@
         </is>
       </c>
       <c r="N227" t="n">
+        <v>42</v>
+      </c>
+      <c r="O227" t="n">
+        <v>42</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
         <v>1</v>
       </c>
-      <c r="O227" t="n">
-        <v>1</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40692,12 +40695,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40731,93 +40734,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>2</v>
-      </c>
-      <c r="P228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R228" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40844,7 +40835,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -40896,98 +40887,18 @@
       <c r="P229" t="n">
         <v>2</v>
       </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R229" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -41081,17 +40992,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41116,7 +41027,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -41130,76 +41041,168 @@
       <c r="O230" t="n">
         <v>2</v>
       </c>
-      <c r="R230" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P230" t="n">
+        <v>2</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41231,12 +41234,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41270,93 +41273,81 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O231" t="n">
-        <v>1</v>
-      </c>
-      <c r="P231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R231" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41374,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -41435,98 +41426,18 @@
       <c r="P232" t="n">
         <v>1</v>
       </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R232" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
@@ -41620,17 +41531,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41655,7 +41566,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -41664,81 +41575,173 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41770,12 +41773,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41809,93 +41812,81 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
-        <v>2</v>
-      </c>
-      <c r="P234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>0.03386531510194095</v>
+        <v>0</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41922,7 +41913,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -41974,98 +41965,18 @@
       <c r="P235" t="n">
         <v>2</v>
       </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R235" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -42159,17 +42070,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42194,7 +42105,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -42203,81 +42114,173 @@
         </is>
       </c>
       <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="n">
+        <v>2</v>
+      </c>
+      <c r="P236" t="n">
+        <v>2</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
         <v>1</v>
       </c>
-      <c r="O236" t="n">
-        <v>1</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42309,12 +42312,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42348,93 +42351,81 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>2</v>
-      </c>
-      <c r="P237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R237" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42461,7 +42452,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -42513,98 +42504,18 @@
       <c r="P238" t="n">
         <v>2</v>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R238" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -42698,17 +42609,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42733,7 +42644,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -42742,81 +42653,173 @@
         </is>
       </c>
       <c r="N239" t="n">
+        <v>2</v>
+      </c>
+      <c r="O239" t="n">
+        <v>2</v>
+      </c>
+      <c r="P239" t="n">
+        <v>2</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
         <v>1</v>
       </c>
-      <c r="O239" t="n">
-        <v>1</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42848,12 +42851,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42878,22 +42881,22 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -42926,42 +42929,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42993,12 +42996,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43023,12 +43026,12 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N241" t="n">
@@ -43037,6 +43040,9 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -43045,14 +43051,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -43062,22 +43063,17 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
         </is>
       </c>
       <c r="AT241" t="n">
@@ -43085,47 +43081,47 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43157,12 +43153,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43187,12 +43183,12 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N242" t="n">
@@ -43201,24 +43197,27 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
         <is>
-          <t>Cinderella disease</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y242" t="inlineStr">
@@ -43228,12 +43227,12 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
@@ -43243,7 +43242,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -43278,12 +43277,12 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
@@ -43301,22 +43300,17 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -43324,47 +43318,47 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43396,12 +43390,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -43474,42 +43468,42 @@
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43541,12 +43535,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -43580,13 +43574,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -43595,7 +43589,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -43615,7 +43609,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -43625,7 +43619,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -43633,47 +43627,47 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43705,12 +43699,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43744,29 +43738,29 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>Meslinger</t>
+          <t>Cinderella disease</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -43791,7 +43785,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -43826,17 +43820,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -43854,7 +43848,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -43864,7 +43858,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -43872,45 +43866,593 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" t="n">
+        <v>1</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV245" t="inlineStr">
+      <c r="AV247" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW245" t="inlineStr">
+      <c r="AW247" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX245" t="inlineStr">
+      <c r="AX247" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY245" t="inlineStr">
+      <c r="AY247" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ245" t="inlineStr">
+      <c r="AZ247" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA245" t="inlineStr">
+      <c r="BA247" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB245" t="inlineStr">
+      <c r="BB247" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC245" t="inlineStr">
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>1</v>
+      </c>
+      <c r="O248" t="n">
+        <v>1</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -44032,7 +44574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -44042,7 +44584,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -44062,7 +44604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -44094,7 +44636,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1451</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -44848,6 +44848,151 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>2</v>
+      </c>
+      <c r="O251" t="n">
+        <v>2</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44881,7 +45026,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -44964,7 +45109,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -44974,7 +45119,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -45026,7 +45171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -40682,12 +40682,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40721,13 +40721,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>0.3924849779879006</v>
+        <v>0</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -40751,7 +40751,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -40759,62 +40759,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40846,12 +40841,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40885,29 +40880,29 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>Mässling</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -40917,7 +40912,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -40932,7 +40927,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -40967,17 +40962,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly measles notifications.</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -40990,7 +40985,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
@@ -40998,62 +40993,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41085,12 +41075,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41115,7 +41105,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -41124,81 +41114,100 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="R230" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41225,17 +41234,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41260,7 +41269,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41269,26 +41278,103 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="O231" t="n">
-        <v>2</v>
-      </c>
-      <c r="P231" t="n">
-        <v>2</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>42</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
@@ -41297,7 +41383,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
@@ -41305,9 +41391,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT231" t="n">
@@ -41315,47 +41406,47 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41382,17 +41473,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41426,173 +41517,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>2</v>
-      </c>
-      <c r="P232" t="n">
-        <v>2</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
         <v>1</v>
       </c>
+      <c r="R232" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41624,12 +41623,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41654,7 +41653,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -41668,76 +41667,88 @@
       <c r="O233" t="n">
         <v>2</v>
       </c>
+      <c r="P233" t="n">
+        <v>2</v>
+      </c>
       <c r="R233" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41764,7 +41775,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -41799,7 +41810,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -41808,26 +41819,106 @@
         </is>
       </c>
       <c r="N234" t="n">
+        <v>2</v>
+      </c>
+      <c r="O234" t="n">
+        <v>2</v>
+      </c>
+      <c r="P234" t="n">
+        <v>2</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
         <v>1</v>
-      </c>
-      <c r="O234" t="n">
-        <v>1</v>
-      </c>
-      <c r="P234" t="n">
-        <v>1</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
@@ -41921,17 +42012,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -41965,173 +42056,81 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
-      </c>
-      <c r="P235" t="n">
-        <v>1</v>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42163,12 +42162,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42193,7 +42192,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -42202,81 +42201,93 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P236" t="n">
+        <v>1</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42303,7 +42314,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -42338,7 +42349,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -42347,26 +42358,106 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P237" t="n">
-        <v>2</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
@@ -42460,17 +42551,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42504,173 +42595,81 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
-        <v>2</v>
-      </c>
-      <c r="P238" t="n">
-        <v>2</v>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42702,12 +42701,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42732,7 +42731,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -42741,81 +42740,93 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O239" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="P239" t="n">
+        <v>2</v>
       </c>
       <c r="R239" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42842,7 +42853,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -42877,7 +42888,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -42894,18 +42905,98 @@
       <c r="P240" t="n">
         <v>2</v>
       </c>
-      <c r="R240" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN240" t="b">
+        <v>1</v>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
@@ -42999,17 +43090,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43043,173 +43134,81 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O241" t="n">
-        <v>2</v>
-      </c>
-      <c r="P241" t="n">
-        <v>2</v>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
         <v>1</v>
       </c>
+      <c r="R241" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43241,12 +43240,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43271,7 +43270,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -43280,81 +43279,93 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O242" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="P242" t="n">
+        <v>2</v>
       </c>
       <c r="R242" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43381,7 +43392,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -43416,7 +43427,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -43425,26 +43436,106 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
+        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -43538,17 +43629,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -43582,173 +43673,81 @@
         </is>
       </c>
       <c r="N244" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="n">
         <v>0</v>
       </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" t="n">
-        <v>0</v>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
-      <c r="AT244" t="n">
-        <v>2</v>
-      </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43780,12 +43779,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43810,12 +43809,12 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N245" t="n">
@@ -43824,6 +43823,9 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -43832,68 +43834,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43920,17 +43931,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43955,12 +43966,12 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N246" t="n">
@@ -43969,23 +43980,101 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="R246" t="n">
+      <c r="P246" t="n">
         <v>0</v>
       </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -43994,22 +44083,17 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_170</t>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -44017,47 +44101,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44084,17 +44168,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44133,170 +44217,76 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
+      <c r="AT247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO247" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP247" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT247" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV247" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44328,12 +44318,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -44380,68 +44370,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44468,17 +44477,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -44512,29 +44521,104 @@
         </is>
       </c>
       <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
         <v>1</v>
       </c>
-      <c r="O249" t="n">
-        <v>1</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44547,7 +44631,7 @@
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
@@ -44557,7 +44641,7 @@
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -44565,47 +44649,47 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44632,17 +44716,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -44676,175 +44760,81 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>1</v>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -44876,118 +44866,521 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="n">
+        <v>1</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="n">
+        <v>1</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>D017</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>麻疹</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N251" t="n">
+      <c r="N253" t="n">
         <v>2</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="R251" t="n">
+      <c r="R253" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S251" t="inlineStr">
+      <c r="S253" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO251" t="inlineStr">
+      <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP251" t="inlineStr">
+      <c r="AP253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
+      <c r="AR253" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS251" t="inlineStr"/>
-      <c r="AT251" t="n">
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
         <v>0</v>
       </c>
-      <c r="AU251" t="inlineStr">
+      <c r="AU253" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV251" t="inlineStr">
+      <c r="AV253" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW251" t="inlineStr">
+      <c r="AW253" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AX253" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
+      <c r="AY253" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ251" t="inlineStr">
+      <c r="AZ253" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA251" t="inlineStr">
+      <c r="BA253" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB251" t="inlineStr">
+      <c r="BB253" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
+      <c r="BC253" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -45109,7 +45502,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -45119,7 +45512,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -45139,7 +45532,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -41114,13 +41114,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O230" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R230" t="n">
-        <v>0.3924849779879006</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -41278,10 +41278,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O231" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -45386,6 +45386,400 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>2</v>
+      </c>
+      <c r="O254" t="n">
+        <v>2</v>
+      </c>
+      <c r="P254" t="n">
+        <v>2</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>2</v>
+      </c>
+      <c r="O255" t="n">
+        <v>2</v>
+      </c>
+      <c r="P255" t="n">
+        <v>2</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45502,7 +45896,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -45512,7 +45906,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -45532,7 +45926,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -45564,7 +45958,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -40134,12 +40134,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40173,13 +40173,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -40212,42 +40212,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -40279,12 +40279,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40331,87 +40331,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40438,7 +40419,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -40487,98 +40468,23 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -40677,17 +40583,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40726,17 +40632,34 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="R228" t="n">
-        <v>0</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -40744,6 +40667,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40751,7 +40732,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -40759,57 +40740,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40836,7 +40822,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -40885,98 +40871,23 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly measles notifications.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -41070,17 +40981,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41114,22 +41025,39 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>41</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.3831400975596171</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -41137,6 +41065,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly measles notifications.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -41144,7 +41130,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
@@ -41152,62 +41138,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41234,7 +41215,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -41283,98 +41264,23 @@
       <c r="O231" t="n">
         <v>41</v>
       </c>
+      <c r="R231" t="n">
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U231" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Mässling</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN231" t="b">
-        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
@@ -41473,17 +41379,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41508,7 +41414,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -41517,81 +41423,175 @@
         </is>
       </c>
       <c r="N232" t="n">
+        <v>41</v>
+      </c>
+      <c r="O232" t="n">
+        <v>41</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
         <v>1</v>
       </c>
-      <c r="O232" t="n">
-        <v>1</v>
-      </c>
-      <c r="R232" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41623,12 +41623,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41662,93 +41662,81 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>2</v>
-      </c>
-      <c r="P233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R233" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41775,7 +41763,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -41827,98 +41815,18 @@
       <c r="P234" t="n">
         <v>2</v>
       </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R234" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
@@ -42012,17 +41920,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -42047,7 +41955,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -42061,76 +41969,168 @@
       <c r="O235" t="n">
         <v>2</v>
       </c>
-      <c r="R235" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P235" t="n">
+        <v>2</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42162,12 +42162,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42201,93 +42201,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
-      </c>
-      <c r="P236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R236" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42314,7 +42302,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -42366,98 +42354,18 @@
       <c r="P237" t="n">
         <v>1</v>
       </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W237" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R237" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE237" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG237" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK237" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM237" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN237" t="b">
-        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
@@ -42551,17 +42459,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42586,7 +42494,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -42595,81 +42503,173 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P238" t="n">
+        <v>1</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42701,12 +42701,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42740,93 +42740,81 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
-        <v>2</v>
-      </c>
-      <c r="P239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>0.03386531510194095</v>
+        <v>0</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42853,7 +42841,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -42905,98 +42893,18 @@
       <c r="P240" t="n">
         <v>2</v>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R240" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN240" t="b">
-        <v>1</v>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
@@ -43090,17 +42998,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43125,7 +43033,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -43134,81 +43042,173 @@
         </is>
       </c>
       <c r="N241" t="n">
+        <v>2</v>
+      </c>
+      <c r="O241" t="n">
+        <v>2</v>
+      </c>
+      <c r="P241" t="n">
+        <v>2</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
         <v>1</v>
       </c>
-      <c r="O241" t="n">
-        <v>1</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43240,12 +43240,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43279,93 +43279,81 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>2</v>
-      </c>
-      <c r="P242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R242" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43392,7 +43380,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -43444,98 +43432,18 @@
       <c r="P243" t="n">
         <v>2</v>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R243" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -43629,17 +43537,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -43664,7 +43572,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -43673,81 +43581,173 @@
         </is>
       </c>
       <c r="N244" t="n">
+        <v>2</v>
+      </c>
+      <c r="O244" t="n">
+        <v>2</v>
+      </c>
+      <c r="P244" t="n">
+        <v>2</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
         <v>1</v>
       </c>
-      <c r="O244" t="n">
-        <v>1</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43779,12 +43779,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43818,93 +43818,81 @@
         </is>
       </c>
       <c r="N245" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" t="n">
+        <v>1</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="n">
         <v>0</v>
       </c>
-      <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="P245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO245" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP245" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
-      <c r="AT245" t="n">
-        <v>2</v>
-      </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43931,7 +43919,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -43983,98 +43971,18 @@
       <c r="P246" t="n">
         <v>0</v>
       </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -44168,17 +44076,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44203,12 +44111,12 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N247" t="n">
@@ -44217,76 +44125,168 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="R247" t="n">
+      <c r="P247" t="n">
         <v>0</v>
       </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44318,12 +44318,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -44370,87 +44370,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44477,7 +44458,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -44526,98 +44507,23 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
@@ -44716,17 +44622,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -44765,76 +44671,170 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44866,12 +44866,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44905,100 +44905,81 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -45025,7 +45006,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -45069,103 +45050,28 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O252" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM252" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN252" t="b">
-        <v>1</v>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
@@ -45264,17 +45170,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -45299,7 +45205,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -45313,76 +45219,170 @@
       <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="R253" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45414,12 +45414,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -45458,88 +45458,76 @@
       <c r="O254" t="n">
         <v>2</v>
       </c>
-      <c r="P254" t="n">
-        <v>2</v>
-      </c>
       <c r="R254" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45566,7 +45554,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -45618,98 +45606,18 @@
       <c r="P255" t="n">
         <v>2</v>
       </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R255" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -45775,6 +45683,782 @@
         </is>
       </c>
       <c r="BC255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>2</v>
+      </c>
+      <c r="O256" t="n">
+        <v>2</v>
+      </c>
+      <c r="P256" t="n">
+        <v>2</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>6</v>
+      </c>
+      <c r="O257" t="n">
+        <v>6</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -45813,7 +46497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -45896,7 +46580,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -45906,7 +46590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -45926,7 +46610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -45958,7 +46642,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1515</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -55137,13 +55137,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O304" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -57241,6 +57241,1093 @@
       <c r="BC315" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>15</v>
+      </c>
+      <c r="O316" t="n">
+        <v>15</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0.01225212611348649</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
+      <c r="AT316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN318" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN320" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AT320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr"/>
+      <c r="AT321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -57277,7 +58364,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -57360,7 +58447,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -57370,7 +58457,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
@@ -57390,7 +58477,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -57422,7 +58509,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1609</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -33989,7 +33989,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -43182,7 +43182,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -51499,7 +51499,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -55830,13 +55830,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O308" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R308" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -55994,10 +55994,10 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O309" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U309" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -58509,7 +58509,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1631</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -68213,6 +68213,151 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="R384" t="n">
+        <v>0</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
+      <c r="AT384" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU384" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -68246,7 +68391,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -68329,7 +68474,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -68339,7 +68484,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
